--- a/artfynd/A 70017-2021 artfynd.xlsx
+++ b/artfynd/A 70017-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 70017-2021 artfynd.xlsx
+++ b/artfynd/A 70017-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -914,6 +914,139 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>125252284</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58381</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>208242</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Mindre vattensalamander</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lissotriton vulgaris</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>v2189, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>640740</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6721244</v>
+      </c>
+      <c r="S4" t="n">
+        <v>85</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Älvkarleby</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>08:44</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>08:44</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Fredrik Söderman</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Fredrik Söderman</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>ÅGP gölgroda</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 70017-2021 artfynd.xlsx
+++ b/artfynd/A 70017-2021 artfynd.xlsx
@@ -919,7 +919,7 @@
         <v>125252284</v>
       </c>
       <c r="B4" t="n">
-        <v>58381</v>
+        <v>58495</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 70017-2021 artfynd.xlsx
+++ b/artfynd/A 70017-2021 artfynd.xlsx
@@ -919,12 +919,7 @@
         <v>125252284</v>
       </c>
       <c r="B4" t="n">
-        <v>58495</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58515</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 70017-2021 artfynd.xlsx
+++ b/artfynd/A 70017-2021 artfynd.xlsx
@@ -919,7 +919,7 @@
         <v>125252284</v>
       </c>
       <c r="B4" t="n">
-        <v>58515</v>
+        <v>58516</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 70017-2021 artfynd.xlsx
+++ b/artfynd/A 70017-2021 artfynd.xlsx
@@ -919,7 +919,7 @@
         <v>125252284</v>
       </c>
       <c r="B4" t="n">
-        <v>58516</v>
+        <v>58517</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 70017-2021 artfynd.xlsx
+++ b/artfynd/A 70017-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,66 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113353737</v>
+        <v>116704993</v>
       </c>
       <c r="B2" t="n">
-        <v>58073</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57258</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100119</v>
+        <v>100065</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gölgroda</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelophylax lessonae</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Camerano, 1882)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>v2189, Upl</t>
+          <t>Västerboda, S, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>640740</v>
+        <v>640716</v>
       </c>
       <c r="R2" t="n">
-        <v>6721244</v>
+        <v>6721283</v>
       </c>
       <c r="S2" t="n">
-        <v>85</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -758,17 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-07-27</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-07-27</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>genom Erik Wallsten, grodvatten planeras</t>
+          <t>I par</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,268 +759,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Nyligen restaurerad göl</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Tommy Löfgren</t>
+          <t>Johan Lilja</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tommy Löfgren</t>
+          <t>Johan Lilja, Fredrik Söderman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>ÅGP gölgroda</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>116704993</v>
-      </c>
-      <c r="B3" t="n">
-        <v>56624</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>100065</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Trana</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Grus grus</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Västerboda, S, Upl</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>640716</v>
-      </c>
-      <c r="R3" t="n">
-        <v>6721283</v>
-      </c>
-      <c r="S3" t="n">
-        <v>25</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Uppsala</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Älvkarleby</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Älvkarleby</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2024-04-23</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2024-04-23</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>I par</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Nyligen restaurerad göl</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Johan Lilja</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Johan Lilja, Fredrik Söderman</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>125252284</v>
-      </c>
-      <c r="B4" t="n">
-        <v>58517</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>208242</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Mindre vattensalamander</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Lissotriton vulgaris</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>i vatten/simmande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>v2189, Upl</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>640740</v>
-      </c>
-      <c r="R4" t="n">
-        <v>6721244</v>
-      </c>
-      <c r="S4" t="n">
-        <v>85</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Uppsala</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Älvkarleby</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Älvkarleby</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2025-05-20</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>08:44</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2025-05-20</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>08:44</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Fredrik Söderman</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Fredrik Söderman</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>ÅGP gölgroda</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 70017-2021 artfynd.xlsx
+++ b/artfynd/A 70017-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,8 +788,16 @@
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116704993</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>